--- a/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2022.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 21:39</t>
+    <t xml:space="preserve">2026-08-21 12:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2022.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21 12:49</t>
+    <t xml:space="preserve">2026-09-04 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -439,7 +439,7 @@
         <v>2018</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>79</v>
+        <v>84.27</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v>2019</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>82.45</v>
+        <v>87.85</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         <v>2020</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>90.59</v>
+        <v>96.74</v>
       </c>
     </row>
     <row r="5">
@@ -463,7 +463,7 @@
         <v>2021</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>100.98</v>
+        <v>107.95</v>
       </c>
     </row>
     <row r="6">
@@ -471,7 +471,7 @@
         <v>2022</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>103.54</v>
+        <v>111.05</v>
       </c>
     </row>
     <row r="7">

--- a/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2022.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 19:49</t>
+    <t xml:space="preserve">2026-09-07 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
